--- a/SuppXLS/Scen_B_RSD_Retrofit-Ctrl.xlsx
+++ b/SuppXLS/Scen_B_RSD_Retrofit-Ctrl.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rbsul\Documents\GitHub\times-ireland-model\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57940FCC-66F0-4E95-A930-1F3949005CA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C31286B-CD24-464F-8C47-7EA9EE5A9C2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{2EA072F4-62CE-45F6-8797-FBD7616D2DDD}"/>
   </bookViews>
@@ -140,7 +140,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="136">
   <si>
     <t>~UC_Sets: T_E:</t>
   </si>
@@ -584,9 +584,6 @@
   </si>
   <si>
     <t>R-RTFT-Det_G,R-RTFT-Det_F,R-RTFT-Det_E,R-RTFT-Det_D,R-RTFT-Det_C,R-RTFT-Det_B3</t>
-  </si>
-  <si>
-    <t>UC_T: UC_RHSRT</t>
   </si>
 </sst>
 </file>
@@ -1359,6 +1356,24 @@
     <xf numFmtId="0" fontId="13" fillId="6" borderId="0" xfId="3" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1394,24 +1409,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -6467,32 +6464,32 @@
     </row>
     <row r="26" spans="1:11" ht="13.5" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="27" spans="1:11" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="C27" s="60" t="s">
+      <c r="C27" s="66" t="s">
         <v>96</v>
       </c>
-      <c r="D27" s="61"/>
-      <c r="E27" s="62"/>
+      <c r="D27" s="67"/>
+      <c r="E27" s="68"/>
       <c r="G27" s="2"/>
       <c r="H27" s="28">
         <v>0.95</v>
       </c>
     </row>
     <row r="28" spans="1:11" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="C28" s="63" t="s">
+      <c r="C28" s="69" t="s">
         <v>97</v>
       </c>
-      <c r="D28" s="64"/>
-      <c r="E28" s="65"/>
+      <c r="D28" s="70"/>
+      <c r="E28" s="71"/>
       <c r="G28" s="28">
         <v>0.75</v>
       </c>
     </row>
     <row r="29" spans="1:11" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="C29" s="66" t="s">
+      <c r="C29" s="72" t="s">
         <v>98</v>
       </c>
-      <c r="D29" s="67"/>
-      <c r="E29" s="68"/>
+      <c r="D29" s="73"/>
+      <c r="E29" s="74"/>
       <c r="F29" s="29">
         <v>0.2</v>
       </c>
@@ -6514,7 +6511,7 @@
     </row>
     <row r="32" spans="1:11" ht="15" x14ac:dyDescent="0.2">
       <c r="D32" s="1" t="s">
-        <v>136</v>
+        <v>72</v>
       </c>
       <c r="G32" s="2"/>
     </row>
@@ -6655,32 +6652,32 @@
       <c r="H37" s="49"/>
     </row>
     <row r="38" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="C38" s="60" t="s">
+      <c r="C38" s="66" t="s">
         <v>130</v>
       </c>
-      <c r="D38" s="61"/>
-      <c r="E38" s="62"/>
+      <c r="D38" s="67"/>
+      <c r="E38" s="68"/>
       <c r="G38" s="2"/>
       <c r="H38" s="28">
         <v>0.25</v>
       </c>
     </row>
     <row r="39" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="C39" s="63" t="s">
+      <c r="C39" s="69" t="s">
         <v>131</v>
       </c>
-      <c r="D39" s="64"/>
-      <c r="E39" s="65"/>
+      <c r="D39" s="70"/>
+      <c r="E39" s="71"/>
       <c r="G39" s="28">
         <v>0.1</v>
       </c>
     </row>
     <row r="40" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="C40" s="66" t="s">
+      <c r="C40" s="72" t="s">
         <v>132</v>
       </c>
-      <c r="D40" s="67"/>
-      <c r="E40" s="68"/>
+      <c r="D40" s="73"/>
+      <c r="E40" s="74"/>
       <c r="F40" s="29">
         <v>0</v>
       </c>
@@ -6704,38 +6701,38 @@
       <c r="G42" s="2"/>
     </row>
     <row r="43" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B43" s="69" t="s">
+      <c r="B43" s="75" t="s">
         <v>102</v>
       </c>
-      <c r="C43" s="70"/>
-      <c r="D43" s="70"/>
-      <c r="E43" s="70"/>
-      <c r="F43" s="70"/>
-      <c r="G43" s="70"/>
-      <c r="H43" s="71"/>
-      <c r="K43" s="72" t="s">
+      <c r="C43" s="76"/>
+      <c r="D43" s="76"/>
+      <c r="E43" s="76"/>
+      <c r="F43" s="76"/>
+      <c r="G43" s="76"/>
+      <c r="H43" s="77"/>
+      <c r="K43" s="60" t="s">
         <v>113</v>
       </c>
-      <c r="L43" s="73"/>
-      <c r="M43" s="74"/>
+      <c r="L43" s="61"/>
+      <c r="M43" s="62"/>
     </row>
     <row r="44" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B44" s="30"/>
-      <c r="C44" s="69">
+      <c r="C44" s="75">
         <v>2018</v>
       </c>
-      <c r="D44" s="70"/>
-      <c r="E44" s="71"/>
-      <c r="F44" s="60">
+      <c r="D44" s="76"/>
+      <c r="E44" s="77"/>
+      <c r="F44" s="66">
         <v>2070</v>
       </c>
-      <c r="G44" s="61"/>
-      <c r="H44" s="62"/>
-      <c r="K44" s="75">
+      <c r="G44" s="67"/>
+      <c r="H44" s="68"/>
+      <c r="K44" s="63">
         <v>0.83330000000000004</v>
       </c>
-      <c r="L44" s="76"/>
-      <c r="M44" s="77"/>
+      <c r="L44" s="64"/>
+      <c r="M44" s="65"/>
     </row>
     <row r="45" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B45" s="43" t="s">
@@ -6996,17 +6993,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="K43:M43"/>
-    <mergeCell ref="K44:M44"/>
-    <mergeCell ref="C38:E38"/>
-    <mergeCell ref="C39:E39"/>
-    <mergeCell ref="C40:E40"/>
     <mergeCell ref="C27:E27"/>
     <mergeCell ref="C28:E28"/>
     <mergeCell ref="C29:E29"/>
     <mergeCell ref="C44:E44"/>
     <mergeCell ref="F44:H44"/>
     <mergeCell ref="B43:H43"/>
+    <mergeCell ref="K43:M43"/>
+    <mergeCell ref="K44:M44"/>
+    <mergeCell ref="C38:E38"/>
+    <mergeCell ref="C39:E39"/>
+    <mergeCell ref="C40:E40"/>
   </mergeCells>
   <phoneticPr fontId="20" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
